--- a/existing_customer/files/recommendations.xlsx
+++ b/existing_customer/files/recommendations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumandeep.a.kaur\Documents\B2B Agentic Screens Demo - Existing Customers\b2b_leadmanagement_ec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhilasha.anand\b2b_streamlit_apps\acquisition\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6397C7B6-D013-4209-9EDB-3C7993368F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539A409A-46A5-44D1-B565-21725A182BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Recommendations" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
   <externalReferences>
     <externalReference r:id="rId3"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Recommendations!$A$4:$Q$27</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="201">
   <si>
     <t>AI Product Recommendations — Up-sell &amp; Cross-sell Opportunities</t>
   </si>
@@ -622,6 +625,24 @@
   </si>
   <si>
     <t>&lt;ul&gt;&lt;li&gt;Education peers adopting basic collaboration tools&lt;/li&gt;&lt;li&gt;Supports remote and hybrid learning models&lt;/li&gt;&lt;li&gt;Low complexity environment&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>Soverign AI Products</t>
+  </si>
+  <si>
+    <t>#4</t>
+  </si>
+  <si>
+    <t>AI Site Safety (Computer Vision)</t>
+  </si>
+  <si>
+    <t>Regulatory pressure on sovereign AI compliance + rapid multi-site expansion</t>
+  </si>
+  <si>
+    <t>Sovereign AI, Site Safety, Compliance-ready, Scalable, Real-time Insights</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt;&lt;li&gt;Regulatory pressure mandates sovereign, on-site AI for safety and compliance&lt;/li&gt;&lt;li&gt;Computer vision generates sensitive operational data requiring in-country processing&lt;/li&gt;&lt;li&gt;Edge-based AI enables low-latency site safety monitoring without reliance on public cloud&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
 </sst>
 </file>
@@ -1198,31 +1219,31 @@
             <v>Mobility</v>
           </cell>
           <cell r="R2" t="str">
-            <v>Networking</v>
+            <v>Network Infrastructure</v>
           </cell>
           <cell r="S2">
             <v>85</v>
           </cell>
           <cell r="T2" t="str">
-            <v>SD-WAN optimisation, Ethernet networking, bandwidth expansion, network modernisation, site connectivity</v>
+            <v>Bandwidth expansion, Ethernet networking, SD-WAN optimization</v>
           </cell>
           <cell r="U2" t="str">
-            <v>IoT &amp; Edge</v>
+            <v>IoT &amp; Asset Management</v>
           </cell>
           <cell r="V2">
             <v>72</v>
           </cell>
           <cell r="W2" t="str">
-            <v>IoT networks, asset monitoring, edge connectivity, device management, remote telemetry</v>
+            <v>Equipment monitoring systems, Heavy equipment fleet management, Construction IoT telemetry, Asset tracking systems, Fleet telematics</v>
           </cell>
           <cell r="X2" t="str">
-            <v>Security</v>
+            <v>AI &amp; Automation</v>
           </cell>
           <cell r="Y2">
             <v>68</v>
           </cell>
           <cell r="Z2" t="str">
-            <v>network security, secure SD-WAN, threat protection, firewall upgrades, perimeter security</v>
+            <v>Construction AI solutions, Site safety automation, AI workforce scheduling, Computer vision construction</v>
           </cell>
           <cell r="AA2" t="str">
             <v>Explicit</v>
@@ -1274,28 +1295,24 @@
           <cell r="P3" t="str">
             <v>Business Internet, Mobility</v>
           </cell>
-          <cell r="Q3"/>
           <cell r="R3" t="str">
             <v>—</v>
           </cell>
           <cell r="S3" t="str">
             <v>—</v>
           </cell>
-          <cell r="T3"/>
           <cell r="U3" t="str">
             <v>—</v>
           </cell>
           <cell r="V3" t="str">
             <v>—</v>
           </cell>
-          <cell r="W3"/>
           <cell r="X3" t="str">
             <v>—</v>
           </cell>
           <cell r="Y3" t="str">
             <v>—</v>
           </cell>
-          <cell r="Z3"/>
           <cell r="AA3" t="str">
             <v>Peer-led</v>
           </cell>
@@ -1506,28 +1523,24 @@
           <cell r="P6" t="str">
             <v>Business Internet</v>
           </cell>
-          <cell r="Q6"/>
           <cell r="R6" t="str">
             <v>—</v>
           </cell>
           <cell r="S6" t="str">
             <v>—</v>
           </cell>
-          <cell r="T6"/>
           <cell r="U6" t="str">
             <v>—</v>
           </cell>
           <cell r="V6" t="str">
             <v>—</v>
           </cell>
-          <cell r="W6"/>
           <cell r="X6" t="str">
             <v>—</v>
           </cell>
           <cell r="Y6" t="str">
             <v>—</v>
           </cell>
-          <cell r="Z6"/>
           <cell r="AA6" t="str">
             <v>Industry-led</v>
           </cell>
@@ -1658,7 +1671,6 @@
           <cell r="P8" t="str">
             <v>Business Internet, SDWAN, Mobility</v>
           </cell>
-          <cell r="Q8"/>
           <cell r="R8" t="str">
             <v>Networking</v>
           </cell>
@@ -1674,14 +1686,12 @@
           <cell r="V8" t="str">
             <v>—</v>
           </cell>
-          <cell r="W8"/>
           <cell r="X8" t="str">
             <v>—</v>
           </cell>
           <cell r="Y8" t="str">
             <v>—</v>
           </cell>
-          <cell r="Z8"/>
           <cell r="AA8" t="str">
             <v>Explicit</v>
           </cell>
@@ -1741,21 +1751,18 @@
           <cell r="S9" t="str">
             <v>—</v>
           </cell>
-          <cell r="T9"/>
           <cell r="U9" t="str">
             <v>—</v>
           </cell>
           <cell r="V9" t="str">
             <v>—</v>
           </cell>
-          <cell r="W9"/>
           <cell r="X9" t="str">
             <v>—</v>
           </cell>
           <cell r="Y9" t="str">
             <v>—</v>
           </cell>
-          <cell r="Z9"/>
           <cell r="AA9" t="str">
             <v>Peer-led</v>
           </cell>
@@ -1886,28 +1893,24 @@
           <cell r="P11" t="str">
             <v>Business Internet, Mobility</v>
           </cell>
-          <cell r="Q11"/>
           <cell r="R11" t="str">
             <v>—</v>
           </cell>
           <cell r="S11" t="str">
             <v>—</v>
           </cell>
-          <cell r="T11"/>
           <cell r="U11" t="str">
             <v>—</v>
           </cell>
           <cell r="V11" t="str">
             <v>—</v>
           </cell>
-          <cell r="W11"/>
           <cell r="X11" t="str">
             <v>—</v>
           </cell>
           <cell r="Y11" t="str">
             <v>—</v>
           </cell>
-          <cell r="Z11"/>
           <cell r="AA11" t="str">
             <v>Industry-led</v>
           </cell>
@@ -2205,11 +2208,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:Q27"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="14" width="25.7109375" customWidth="1"/>
-    <col min="15" max="16" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="14" width="25.6640625" customWidth="1"/>
+    <col min="15" max="16" width="58.88671875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2243,7 +2246,7 @@
       <c r="J2" s="47"/>
       <c r="K2" s="47"/>
     </row>
-    <row r="4" spans="1:17" ht="21.95" customHeight="1">
+    <row r="4" spans="1:17" ht="21.9" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2296,7 +2299,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="51">
+    <row r="5" spans="1:17" ht="52.8">
       <c r="A5" s="2" t="s">
         <v>169</v>
       </c>
@@ -2353,7 +2356,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="51">
+    <row r="6" spans="1:17" ht="52.8">
       <c r="A6" s="2" t="s">
         <v>169</v>
       </c>
@@ -2410,7 +2413,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="51">
+    <row r="7" spans="1:17" ht="52.8">
       <c r="A7" s="2" t="s">
         <v>169</v>
       </c>
@@ -2467,68 +2470,68 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="51">
-      <c r="A8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2" t="str">
+    <row r="8" spans="1:17" ht="66">
+      <c r="A8" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="16" t="str">
         <f>VLOOKUP(B8,[1]Complete!$B$1:$F$11,3,0)</f>
-        <v>Transport &amp; Logistics</v>
-      </c>
-      <c r="D8" s="2" t="str">
+        <v>Construction</v>
+      </c>
+      <c r="D8" s="16" t="str">
         <f>VLOOKUP(B8,[1]Complete!$B$1:$F$11,5,0)</f>
-        <v>150–300</v>
-      </c>
-      <c r="E8" s="2" t="str">
+        <v>500–1000</v>
+      </c>
+      <c r="E8" s="16" t="str">
         <f>VLOOKUP(B8,[1]Complete!$B$1:$F$11,2,0)</f>
-        <v>Fremantle, WA</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>41</v>
+        <v>Newcastle, NSW</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="G8" s="43" t="str">
         <f>VLOOKUP(B8,[1]Complete!$B$1:$AA$11,26,0)</f>
-        <v>Peer-led</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>43</v>
+        <v>Explicit</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>46</v>
+        <v>121</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="O8" s="45" t="s">
-        <v>176</v>
-      </c>
-      <c r="P8" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q8" s="11" t="s">
-        <v>48</v>
+        <v>200</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>199</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="51">
-      <c r="A9" s="16" t="s">
+    <row r="9" spans="1:17" ht="39.6">
+      <c r="A9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="11" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="2" t="str">
@@ -2543,7 +2546,7 @@
         <f>VLOOKUP(B9,[1]Complete!$B$1:$F$11,2,0)</f>
         <v>Fremantle, WA</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="11" t="s">
         <v>41</v>
       </c>
       <c r="G9" s="43" t="str">
@@ -2553,96 +2556,96 @@
       <c r="H9" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>33</v>
+      <c r="I9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="O9" s="45" t="s">
-        <v>177</v>
-      </c>
-      <c r="P9" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q9" s="16" t="s">
-        <v>38</v>
+        <v>176</v>
+      </c>
+      <c r="P9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="51">
-      <c r="A10" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>53</v>
+    <row r="10" spans="1:17" ht="39.6">
+      <c r="A10" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>40</v>
       </c>
       <c r="C10" s="2" t="str">
         <f>VLOOKUP(B10,[1]Complete!$B$1:$F$11,3,0)</f>
-        <v>Energy</v>
+        <v>Transport &amp; Logistics</v>
       </c>
       <c r="D10" s="2" t="str">
         <f>VLOOKUP(B10,[1]Complete!$B$1:$F$11,5,0)</f>
-        <v>1000+</v>
+        <v>150–300</v>
       </c>
       <c r="E10" s="2" t="str">
         <f>VLOOKUP(B10,[1]Complete!$B$1:$F$11,2,0)</f>
-        <v>Adelaide, SA</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>54</v>
+        <v>Fremantle, WA</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>41</v>
       </c>
       <c r="G10" s="43" t="str">
         <f>VLOOKUP(B10,[1]Complete!$B$1:$AA$11,26,0)</f>
-        <v>Explicit</v>
+        <v>Peer-led</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>56</v>
+      <c r="I10" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M10" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>50</v>
       </c>
       <c r="O10" s="45" t="s">
-        <v>178</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q10" s="11" t="s">
-        <v>24</v>
+        <v>177</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q10" s="16" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="51">
-      <c r="A11" s="16" t="s">
+    <row r="11" spans="1:17" ht="52.8">
+      <c r="A11" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="11" t="s">
         <v>53</v>
       </c>
       <c r="C11" s="2" t="str">
@@ -2657,7 +2660,7 @@
         <f>VLOOKUP(B11,[1]Complete!$B$1:$F$11,2,0)</f>
         <v>Adelaide, SA</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="11" t="s">
         <v>54</v>
       </c>
       <c r="G11" s="43" t="str">
@@ -2667,39 +2670,39 @@
       <c r="H11" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="M11" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>61</v>
+      <c r="I11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="O11" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q11" s="16" t="s">
-        <v>63</v>
+        <v>178</v>
+      </c>
+      <c r="P11" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="38.25">
-      <c r="A12" s="11" t="s">
+    <row r="12" spans="1:17" ht="52.8">
+      <c r="A12" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="16" t="s">
         <v>53</v>
       </c>
       <c r="C12" s="2" t="str">
@@ -2714,7 +2717,7 @@
         <f>VLOOKUP(B12,[1]Complete!$B$1:$F$11,2,0)</f>
         <v>Adelaide, SA</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="16" t="s">
         <v>54</v>
       </c>
       <c r="G12" s="43" t="str">
@@ -2724,14 +2727,14 @@
       <c r="H12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I12" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>64</v>
+      <c r="I12" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>58</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L12" s="21" t="s">
         <v>60</v>
@@ -2739,40 +2742,40 @@
       <c r="M12" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="N12" s="11" t="s">
-        <v>66</v>
+      <c r="N12" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="O12" s="45" t="s">
-        <v>180</v>
-      </c>
-      <c r="P12" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q12" s="11" t="s">
-        <v>68</v>
+        <v>179</v>
+      </c>
+      <c r="P12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q12" s="16" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="38.25">
-      <c r="A13" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>70</v>
+    <row r="13" spans="1:17" ht="39.6">
+      <c r="A13" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>53</v>
       </c>
       <c r="C13" s="2" t="str">
         <f>VLOOKUP(B13,[1]Complete!$B$1:$F$11,3,0)</f>
-        <v>Healthcare</v>
+        <v>Energy</v>
       </c>
       <c r="D13" s="2" t="str">
         <f>VLOOKUP(B13,[1]Complete!$B$1:$F$11,5,0)</f>
-        <v>300–500</v>
+        <v>1000+</v>
       </c>
       <c r="E13" s="2" t="str">
         <f>VLOOKUP(B13,[1]Complete!$B$1:$F$11,2,0)</f>
-        <v>Melbourne, VIC</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>71</v>
+        <v>Adelaide, SA</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="G13" s="43" t="str">
         <f>VLOOKUP(B13,[1]Complete!$B$1:$AA$11,26,0)</f>
@@ -2781,39 +2784,39 @@
       <c r="H13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="K13" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="M13" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="N13" s="16" t="s">
-        <v>75</v>
+      <c r="I13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>66</v>
       </c>
       <c r="O13" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="P13" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>77</v>
+        <v>180</v>
+      </c>
+      <c r="P13" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="51">
-      <c r="A14" s="11" t="s">
+    <row r="14" spans="1:17" ht="39.6">
+      <c r="A14" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="16" t="s">
         <v>70</v>
       </c>
       <c r="C14" s="2" t="str">
@@ -2828,7 +2831,7 @@
         <f>VLOOKUP(B14,[1]Complete!$B$1:$F$11,2,0)</f>
         <v>Melbourne, VIC</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="16" t="s">
         <v>71</v>
       </c>
       <c r="G14" s="43" t="str">
@@ -2838,128 +2841,128 @@
       <c r="H14" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I14" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="M14" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" s="11" t="s">
-        <v>81</v>
+      <c r="I14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N14" s="16" t="s">
+        <v>75</v>
       </c>
       <c r="O14" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="P14" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q14" s="11" t="s">
-        <v>83</v>
+        <v>181</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q14" s="16" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="38.25">
-      <c r="A15" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>85</v>
+    <row r="15" spans="1:17" ht="52.8">
+      <c r="A15" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C15" s="2" t="str">
         <f>VLOOKUP(B15,[1]Complete!$B$1:$F$11,3,0)</f>
-        <v>Agriculture</v>
+        <v>Healthcare</v>
       </c>
       <c r="D15" s="2" t="str">
         <f>VLOOKUP(B15,[1]Complete!$B$1:$F$11,5,0)</f>
-        <v>50–150</v>
+        <v>300–500</v>
       </c>
       <c r="E15" s="2" t="str">
         <f>VLOOKUP(B15,[1]Complete!$B$1:$F$11,2,0)</f>
-        <v>Toowoomba, QLD</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>86</v>
+        <v>Melbourne, VIC</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="G15" s="43" t="str">
         <f>VLOOKUP(B15,[1]Complete!$B$1:$AA$11,26,0)</f>
-        <v>Industry-led</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="K15" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="L15" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="N15" s="16" t="s">
-        <v>90</v>
+        <v>Explicit</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="M15" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="O15" s="45" t="s">
-        <v>183</v>
-      </c>
-      <c r="P15" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q15" s="16" t="s">
-        <v>92</v>
+        <v>182</v>
+      </c>
+      <c r="P15" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="38.25">
-      <c r="A16" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>94</v>
+    <row r="16" spans="1:17" ht="39.6">
+      <c r="A16" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>85</v>
       </c>
       <c r="C16" s="2" t="str">
         <f>VLOOKUP(B16,[1]Complete!$B$1:$F$11,3,0)</f>
-        <v>Manufacturing</v>
+        <v>Agriculture</v>
       </c>
       <c r="D16" s="2" t="str">
         <f>VLOOKUP(B16,[1]Complete!$B$1:$F$11,5,0)</f>
-        <v>1000+</v>
+        <v>50–150</v>
       </c>
       <c r="E16" s="2" t="str">
         <f>VLOOKUP(B16,[1]Complete!$B$1:$F$11,2,0)</f>
-        <v>Geelong, VIC</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>95</v>
+        <v>Toowoomba, QLD</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>86</v>
       </c>
       <c r="G16" s="43" t="str">
         <f>VLOOKUP(B16,[1]Complete!$B$1:$AA$11,26,0)</f>
-        <v>Explicit</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="11" t="s">
+        <v>Industry-led</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="I16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="K16" s="19" t="s">
-        <v>97</v>
+      <c r="J16" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>89</v>
       </c>
       <c r="L16" s="20" t="s">
         <v>20</v>
@@ -2967,24 +2970,24 @@
       <c r="M16" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="N16" s="11" t="s">
-        <v>98</v>
+      <c r="N16" s="16" t="s">
+        <v>90</v>
       </c>
       <c r="O16" s="45" t="s">
-        <v>184</v>
-      </c>
-      <c r="P16" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q16" s="11" t="s">
-        <v>100</v>
+        <v>183</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q16" s="16" t="s">
+        <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="38.25">
-      <c r="A17" s="16" t="s">
+    <row r="17" spans="1:17" ht="39.6">
+      <c r="A17" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="11" t="s">
         <v>94</v>
       </c>
       <c r="C17" s="2" t="str">
@@ -2999,7 +3002,7 @@
         <f>VLOOKUP(B17,[1]Complete!$B$1:$F$11,2,0)</f>
         <v>Geelong, VIC</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="11" t="s">
         <v>95</v>
       </c>
       <c r="G17" s="43" t="str">
@@ -3009,39 +3012,39 @@
       <c r="H17" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="16" t="s">
-        <v>101</v>
+      <c r="I17" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>96</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="L17" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="M17" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="N17" s="16" t="s">
-        <v>103</v>
+        <v>97</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>98</v>
       </c>
       <c r="O17" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="P17" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q17" s="16" t="s">
-        <v>105</v>
+        <v>184</v>
+      </c>
+      <c r="P17" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q17" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="38.25">
-      <c r="A18" s="11" t="s">
+    <row r="18" spans="1:17" ht="39.6">
+      <c r="A18" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="16" t="s">
         <v>94</v>
       </c>
       <c r="C18" s="2" t="str">
@@ -3056,7 +3059,7 @@
         <f>VLOOKUP(B18,[1]Complete!$B$1:$F$11,2,0)</f>
         <v>Geelong, VIC</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="16" t="s">
         <v>95</v>
       </c>
       <c r="G18" s="43" t="str">
@@ -3066,96 +3069,96 @@
       <c r="H18" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I18" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="L18" s="21" t="s">
-        <v>60</v>
+      <c r="I18" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="M18" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="11" t="s">
-        <v>107</v>
+      <c r="N18" s="16" t="s">
+        <v>103</v>
       </c>
       <c r="O18" s="45" t="s">
-        <v>186</v>
-      </c>
-      <c r="P18" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q18" s="11" t="s">
-        <v>68</v>
+        <v>185</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="38.25">
-      <c r="A19" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>110</v>
+    <row r="19" spans="1:17" ht="39.6">
+      <c r="A19" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="C19" s="2" t="str">
         <f>VLOOKUP(B19,[1]Complete!$B$1:$F$11,3,0)</f>
-        <v>Construction</v>
+        <v>Manufacturing</v>
       </c>
       <c r="D19" s="2" t="str">
         <f>VLOOKUP(B19,[1]Complete!$B$1:$F$11,5,0)</f>
-        <v>150–300</v>
+        <v>1000+</v>
       </c>
       <c r="E19" s="2" t="str">
         <f>VLOOKUP(B19,[1]Complete!$B$1:$F$11,2,0)</f>
-        <v>Gold Coast, QLD</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>15</v>
+        <v>Geelong, VIC</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>95</v>
       </c>
       <c r="G19" s="43" t="str">
         <f>VLOOKUP(B19,[1]Complete!$B$1:$AA$11,26,0)</f>
         <v>Explicit</v>
       </c>
-      <c r="H19" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K19" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="L19" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="N19" s="16" t="s">
-        <v>112</v>
+      <c r="H19" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="M19" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="O19" s="45" t="s">
-        <v>187</v>
-      </c>
-      <c r="P19" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q19" s="16" t="s">
-        <v>114</v>
+        <v>186</v>
+      </c>
+      <c r="P19" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="38.25">
-      <c r="A20" s="11" t="s">
+    <row r="20" spans="1:17" ht="39.6">
+      <c r="A20" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="16" t="s">
         <v>110</v>
       </c>
       <c r="C20" s="2" t="str">
@@ -3170,7 +3173,7 @@
         <f>VLOOKUP(B20,[1]Complete!$B$1:$F$11,2,0)</f>
         <v>Gold Coast, QLD</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="16" t="s">
         <v>15</v>
       </c>
       <c r="G20" s="43" t="str">
@@ -3180,96 +3183,96 @@
       <c r="H20" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I20" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="L20" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="M20" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="11" t="s">
-        <v>116</v>
+      <c r="I20" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N20" s="16" t="s">
+        <v>112</v>
       </c>
       <c r="O20" s="45" t="s">
-        <v>188</v>
-      </c>
-      <c r="P20" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q20" s="11" t="s">
-        <v>38</v>
+        <v>187</v>
+      </c>
+      <c r="P20" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q20" s="16" t="s">
+        <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="38.25">
-      <c r="A21" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>119</v>
+    <row r="21" spans="1:17" ht="39.6">
+      <c r="A21" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>110</v>
       </c>
       <c r="C21" s="2" t="str">
         <f>VLOOKUP(B21,[1]Complete!$B$1:$F$11,3,0)</f>
-        <v>Financial Services</v>
+        <v>Construction</v>
       </c>
       <c r="D21" s="2" t="str">
         <f>VLOOKUP(B21,[1]Complete!$B$1:$F$11,5,0)</f>
-        <v>50–150</v>
+        <v>150–300</v>
       </c>
       <c r="E21" s="2" t="str">
         <f>VLOOKUP(B21,[1]Complete!$B$1:$F$11,2,0)</f>
-        <v>Sydney, NSW</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>120</v>
+        <v>Gold Coast, QLD</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="G21" s="43" t="str">
         <f>VLOOKUP(B21,[1]Complete!$B$1:$AA$11,26,0)</f>
-        <v>Peer-led</v>
+        <v>Explicit</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I21" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>43</v>
+      <c r="I21" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="L21" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="M21" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="N21" s="16" t="s">
-        <v>122</v>
+        <v>115</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="M21" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="11" t="s">
+        <v>116</v>
       </c>
       <c r="O21" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="P21" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q21" s="16" t="s">
-        <v>48</v>
+        <v>188</v>
+      </c>
+      <c r="P21" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="38.25">
-      <c r="A22" s="11" t="s">
+    <row r="22" spans="1:17" ht="39.6">
+      <c r="A22" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="16" t="s">
         <v>119</v>
       </c>
       <c r="C22" s="2" t="str">
@@ -3284,7 +3287,7 @@
         <f>VLOOKUP(B22,[1]Complete!$B$1:$F$11,2,0)</f>
         <v>Sydney, NSW</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="16" t="s">
         <v>120</v>
       </c>
       <c r="G22" s="43" t="str">
@@ -3294,92 +3297,92 @@
       <c r="H22" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I22" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>72</v>
+      <c r="I22" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>43</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="L22" s="15" t="s">
-        <v>74</v>
+        <v>121</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>45</v>
       </c>
       <c r="M22" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="N22" s="11" t="s">
-        <v>125</v>
+      <c r="N22" s="16" t="s">
+        <v>122</v>
       </c>
       <c r="O22" s="45" t="s">
-        <v>190</v>
-      </c>
-      <c r="P22" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q22" s="11" t="s">
-        <v>127</v>
+        <v>189</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q22" s="16" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="38.25">
-      <c r="A23" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>128</v>
+    <row r="23" spans="1:17" ht="39.6">
+      <c r="A23" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="C23" s="2" t="str">
         <f>VLOOKUP(B23,[1]Complete!$B$1:$F$11,3,0)</f>
-        <v>Mining</v>
+        <v>Financial Services</v>
       </c>
       <c r="D23" s="2" t="str">
         <f>VLOOKUP(B23,[1]Complete!$B$1:$F$11,5,0)</f>
-        <v>500–1000</v>
+        <v>50–150</v>
       </c>
       <c r="E23" s="2" t="str">
         <f>VLOOKUP(B23,[1]Complete!$B$1:$F$11,2,0)</f>
-        <v>Perth, WA</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>129</v>
+        <v>Sydney, NSW</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="G23" s="43" t="str">
         <f>VLOOKUP(B23,[1]Complete!$B$1:$AA$11,26,0)</f>
-        <v>Explicit</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="L23" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M23" s="8" t="s">
+        <v>Peer-led</v>
+      </c>
+      <c r="H23" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="M23" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>132</v>
+      <c r="N23" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="O23" s="45" t="s">
-        <v>191</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>38</v>
+        <v>190</v>
+      </c>
+      <c r="P23" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q23" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="38.25">
+    <row r="24" spans="1:17" ht="39.6">
       <c r="A24" s="2" t="s">
         <v>170</v>
       </c>
@@ -3409,95 +3412,95 @@
         <v>16</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K24" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>21</v>
+        <v>131</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O24" s="45" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="38.25">
-      <c r="A25" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>138</v>
+    <row r="25" spans="1:17" ht="39.6">
+      <c r="A25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="C25" s="2" t="str">
         <f>VLOOKUP(B25,[1]Complete!$B$1:$F$11,3,0)</f>
-        <v>Education</v>
+        <v>Mining</v>
       </c>
       <c r="D25" s="2" t="str">
         <f>VLOOKUP(B25,[1]Complete!$B$1:$F$11,5,0)</f>
-        <v>&lt;50</v>
+        <v>500–1000</v>
       </c>
       <c r="E25" s="2" t="str">
         <f>VLOOKUP(B25,[1]Complete!$B$1:$F$11,2,0)</f>
-        <v>Parramatta, NSW</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>139</v>
+        <v>Perth, WA</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="G25" s="43" t="str">
         <f>VLOOKUP(B25,[1]Complete!$B$1:$AA$11,26,0)</f>
-        <v>Industry-led</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="K25" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="L25" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="M25" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>141</v>
+        <v>Explicit</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="O25" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="P25" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q25" s="11" t="s">
-        <v>92</v>
+        <v>192</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="38.25">
-      <c r="A26" s="16" t="s">
+    <row r="26" spans="1:17" ht="39.6">
+      <c r="A26" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="11" t="s">
         <v>138</v>
       </c>
       <c r="C26" s="2" t="str">
@@ -3512,7 +3515,7 @@
         <f>VLOOKUP(B26,[1]Complete!$B$1:$F$11,2,0)</f>
         <v>Parramatta, NSW</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="11" t="s">
         <v>139</v>
       </c>
       <c r="G26" s="43" t="str">
@@ -3522,35 +3525,93 @@
       <c r="H26" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="I26" s="16" t="s">
+      <c r="I26" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="K26" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="M26" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="O26" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="P26" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q26" s="11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="39.6">
+      <c r="A27" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" s="2" t="str">
+        <f>VLOOKUP(B27,[1]Complete!$B$1:$F$11,3,0)</f>
+        <v>Education</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f>VLOOKUP(B27,[1]Complete!$B$1:$F$11,5,0)</f>
+        <v>&lt;50</v>
+      </c>
+      <c r="E27" s="2" t="str">
+        <f>VLOOKUP(B27,[1]Complete!$B$1:$F$11,2,0)</f>
+        <v>Parramatta, NSW</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="G27" s="43" t="str">
+        <f>VLOOKUP(B27,[1]Complete!$B$1:$AA$11,26,0)</f>
+        <v>Industry-led</v>
+      </c>
+      <c r="H27" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="I27" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="J26" s="16" t="s">
+      <c r="J27" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="K26" s="23" t="s">
+      <c r="K27" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="L26" s="15" t="s">
+      <c r="L27" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="M26" s="18" t="s">
+      <c r="M27" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="N26" s="16" t="s">
+      <c r="N27" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="O26" s="45" t="s">
+      <c r="O27" s="45" t="s">
         <v>194</v>
       </c>
-      <c r="P26" s="16" t="s">
+      <c r="P27" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="Q26" s="16" t="s">
+      <c r="Q27" s="16" t="s">
         <v>146</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:Q27" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
@@ -3562,7 +3623,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3580,7 +3641,7 @@
       <c r="E1" s="47"/>
       <c r="F1" s="47"/>
     </row>
-    <row r="3" spans="1:6" ht="27.75">
+    <row r="3" spans="1:6" ht="28.2">
       <c r="A3" s="25" t="s">
         <v>148</v>
       </c>
@@ -3597,7 +3658,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="36">
+    <row r="4" spans="1:6" ht="34.200000000000003">
       <c r="A4" s="30" t="s">
         <v>153</v>
       </c>
@@ -3614,7 +3675,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75">
+    <row r="6" spans="1:6" ht="15.6">
       <c r="A6" s="35" t="s">
         <v>158</v>
       </c>
